--- a/جميع المواد.xlsx
+++ b/جميع المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6081673F-B36E-4C63-B9BB-943934398BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F36BA7-3987-45BC-8E73-FA0D85B6C0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" xr2:uid="{EBC31ABE-D4D8-4E62-9EC4-0F938495CB12}"/>
   </bookViews>
@@ -22646,48 +22646,6 @@
     <cellStyle name="عادي 2" xfId="1" xr:uid="{51AF0A44-A7B8-40FA-A372-D83B99473500}"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -23129,13 +23087,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -23177,6 +23128,55 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="0"/>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -23191,19 +23191,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{249BB913-5864-4EE3-9B6C-18CCC10825A5}" name="الجدول1" displayName="الجدول1" ref="A1:J1889" totalsRowShown="0" headerRowDxfId="0" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11" headerRowCellStyle="عادي 2" dataCellStyle="عادي 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{249BB913-5864-4EE3-9B6C-18CCC10825A5}" name="الجدول1" displayName="الجدول1" ref="A1:J1889" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10" headerRowCellStyle="عادي 2" dataCellStyle="عادي 2">
   <autoFilter ref="A1:J1889" xr:uid="{249BB913-5864-4EE3-9B6C-18CCC10825A5}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1390FAD9-1639-4DEC-B612-64AACAD8C8CB}" name="#" dataDxfId="10" dataCellStyle="عادي 2"/>
-    <tableColumn id="2" xr3:uid="{2FAB6257-24C7-419F-9EE3-024168A1624D}" name="الرمز" dataDxfId="9" dataCellStyle="عادي 2"/>
-    <tableColumn id="3" xr3:uid="{A561E0A7-A01C-493D-B231-425B8DBDEAC0}" name="اسم المادة" dataDxfId="8" dataCellStyle="عادي 2"/>
-    <tableColumn id="4" xr3:uid="{F7CA75CA-8FCC-4533-A062-7525FE71D031}" name="الوحدة" dataDxfId="7" dataCellStyle="عادي 2"/>
-    <tableColumn id="5" xr3:uid="{C4C48D41-080D-4D7D-B6B1-55268A59F200}" name="سعر المبيع" dataDxfId="6" dataCellStyle="عادي 2"/>
-    <tableColumn id="6" xr3:uid="{37552D83-6ED6-4343-B5C5-0618434735F0}" name="بطاقة مجموعة" dataDxfId="5" dataCellStyle="عادي 2"/>
-    <tableColumn id="7" xr3:uid="{926EE332-50B9-4133-8438-5E0BC7AE7570}" name="الاسم اللاتيني" dataDxfId="4" dataCellStyle="عادي 2"/>
-    <tableColumn id="8" xr3:uid="{A84A00E3-8DD4-4EF7-83D2-5A83D58B2906}" name="الكمية" dataDxfId="3" dataCellStyle="عادي 2"/>
-    <tableColumn id="9" xr3:uid="{FC005039-E823-4F38-B669-5ECA82A0C7ED}" name="سعر الشراء" dataDxfId="2" dataCellStyle="عادي 2"/>
-    <tableColumn id="10" xr3:uid="{585093D5-93AB-41E6-9390-869E820DACA9}" name="الباركود" dataDxfId="1" dataCellStyle="عادي 2"/>
+    <tableColumn id="1" xr3:uid="{1390FAD9-1639-4DEC-B612-64AACAD8C8CB}" name="#" dataDxfId="9" dataCellStyle="عادي 2"/>
+    <tableColumn id="2" xr3:uid="{2FAB6257-24C7-419F-9EE3-024168A1624D}" name="الرمز" dataDxfId="8" dataCellStyle="عادي 2"/>
+    <tableColumn id="3" xr3:uid="{A561E0A7-A01C-493D-B231-425B8DBDEAC0}" name="اسم المادة" dataDxfId="7" dataCellStyle="عادي 2"/>
+    <tableColumn id="4" xr3:uid="{F7CA75CA-8FCC-4533-A062-7525FE71D031}" name="الوحدة" dataDxfId="6" dataCellStyle="عادي 2"/>
+    <tableColumn id="5" xr3:uid="{C4C48D41-080D-4D7D-B6B1-55268A59F200}" name="سعر المبيع" dataDxfId="5" dataCellStyle="عادي 2"/>
+    <tableColumn id="6" xr3:uid="{37552D83-6ED6-4343-B5C5-0618434735F0}" name="بطاقة مجموعة" dataDxfId="4" dataCellStyle="عادي 2"/>
+    <tableColumn id="7" xr3:uid="{926EE332-50B9-4133-8438-5E0BC7AE7570}" name="الاسم اللاتيني" dataDxfId="3" dataCellStyle="عادي 2"/>
+    <tableColumn id="8" xr3:uid="{A84A00E3-8DD4-4EF7-83D2-5A83D58B2906}" name="الكمية" dataDxfId="2" dataCellStyle="عادي 2"/>
+    <tableColumn id="9" xr3:uid="{FC005039-E823-4F38-B669-5ECA82A0C7ED}" name="سعر الشراء" dataDxfId="1" dataCellStyle="عادي 2"/>
+    <tableColumn id="10" xr3:uid="{585093D5-93AB-41E6-9390-869E820DACA9}" name="الباركود" dataDxfId="0" dataCellStyle="عادي 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
